--- a/data/trans_orig/P33_1_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P33_1_2023-Provincia-trans_orig.xlsx
@@ -489,7 +489,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Número medio de horas que duerme habitualmente al día entre semana</t>
+          <t>Número medio de horas que duerme habitualmente al día entre semana (tasa de respuesta: 97,4%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,0; 7,35</t>
+          <t>7,0; 7,33</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,78; 7,01</t>
+          <t>6,8; 7,02</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,95; 7,16</t>
+          <t>6,94; 7,16</t>
         </is>
       </c>
     </row>
@@ -621,17 +621,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,1; 7,36</t>
+          <t>7,1; 7,37</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,16; 7,37</t>
+          <t>7,16; 7,39</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,16; 7,33</t>
+          <t>7,17; 7,33</t>
         </is>
       </c>
     </row>
@@ -671,17 +671,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,96; 7,21</t>
+          <t>6,95; 7,22</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,78; 7,02</t>
+          <t>6,8; 7,03</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,92; 7,09</t>
+          <t>6,91; 7,08</t>
         </is>
       </c>
     </row>
@@ -721,17 +721,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,89; 7,21</t>
+          <t>6,86; 7,2</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,79; 7,01</t>
+          <t>6,78; 7,01</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,87; 7,06</t>
+          <t>6,87; 7,05</t>
         </is>
       </c>
     </row>
@@ -771,7 +771,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>6,67; 6,92</t>
+          <t>6,66; 6,91</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,59; 6,76</t>
+          <t>6,6; 6,76</t>
         </is>
       </c>
     </row>
@@ -821,12 +821,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6,89; 7,12</t>
+          <t>6,9; 7,12</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6,69; 6,94</t>
+          <t>6,68; 6,94</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -871,17 +871,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>6,77; 7,0</t>
+          <t>6,8; 7,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>6,3; 6,85</t>
+          <t>6,31; 6,85</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6,48; 6,88</t>
+          <t>6,47; 6,88</t>
         </is>
       </c>
     </row>
@@ -921,7 +921,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>7,4; 7,82</t>
+          <t>7,4; 7,8</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7,36; 7,68</t>
+          <t>7,36; 7,66</t>
         </is>
       </c>
     </row>
@@ -976,12 +976,12 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>6,77; 7,01</t>
+          <t>6,75; 7,01</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>6,97; 7,14</t>
+          <t>6,97; 7,15</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P33_1_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P33_1_2023-Provincia-trans_orig.xlsx
@@ -548,17 +548,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>7,16</t>
+          <t>7,14</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>6,91</t>
+          <t>6,98</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7,04</t>
+          <t>7,06</t>
         </is>
       </c>
     </row>
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,0; 7,33</t>
+          <t>7,0; 7,26</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,8; 7,02</t>
+          <t>6,88; 7,11</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,94; 7,16</t>
+          <t>6,98; 7,15</t>
         </is>
       </c>
     </row>
@@ -598,17 +598,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>7,22</t>
+          <t>7,24</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>7,27</t>
+          <t>7,26</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7,24</t>
+          <t>7,25</t>
         </is>
       </c>
     </row>
@@ -621,12 +621,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,1; 7,37</t>
+          <t>7,1; 7,36</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,16; 7,39</t>
+          <t>7,16; 7,37</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -648,17 +648,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>7,09</t>
+          <t>7,07</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>6,92</t>
+          <t>6,9</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>7,0</t>
+          <t>6,98</t>
         </is>
       </c>
     </row>
@@ -671,17 +671,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,95; 7,22</t>
+          <t>6,92; 7,18</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,8; 7,03</t>
+          <t>6,8; 7,02</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,91; 7,08</t>
+          <t>6,9; 7,06</t>
         </is>
       </c>
     </row>
@@ -698,17 +698,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>7,04</t>
+          <t>7,02</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>6,91</t>
+          <t>6,89</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6,96</t>
+          <t>6,95</t>
         </is>
       </c>
     </row>
@@ -721,17 +721,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,86; 7,2</t>
+          <t>6,86; 7,17</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,78; 7,01</t>
+          <t>6,76; 7,02</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,87; 7,05</t>
+          <t>6,85; 7,04</t>
         </is>
       </c>
     </row>
@@ -748,17 +748,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>6,79</t>
+          <t>6,81</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>6,57</t>
+          <t>6,58</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6,67</t>
+          <t>6,69</t>
         </is>
       </c>
     </row>
@@ -771,17 +771,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>6,66; 6,91</t>
+          <t>6,7; 6,93</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6,48; 6,68</t>
+          <t>6,48; 6,7</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,6; 6,76</t>
+          <t>6,61; 6,77</t>
         </is>
       </c>
     </row>
@@ -803,12 +803,12 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>6,82</t>
+          <t>6,8</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>6,92</t>
+          <t>6,91</t>
         </is>
       </c>
     </row>
@@ -821,17 +821,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6,9; 7,12</t>
+          <t>6,89; 7,12</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6,68; 6,94</t>
+          <t>6,68; 6,93</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6,84; 7,0</t>
+          <t>6,82; 7,0</t>
         </is>
       </c>
     </row>
@@ -848,17 +848,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>6,89</t>
+          <t>6,93</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>6,62</t>
+          <t>6,82</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6,74</t>
+          <t>6,87</t>
         </is>
       </c>
     </row>
@@ -871,17 +871,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>6,8; 7,0</t>
+          <t>6,83; 7,03</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>6,31; 6,85</t>
+          <t>6,74; 6,9</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6,47; 6,88</t>
+          <t>6,8; 6,94</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>7,57</t>
+          <t>7,43</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>7,46</t>
+          <t>7,38</t>
         </is>
       </c>
     </row>
@@ -921,7 +921,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>7,4; 7,8</t>
+          <t>7,38; 7,49</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7,36; 7,66</t>
+          <t>7,33; 7,42</t>
         </is>
       </c>
     </row>
@@ -948,12 +948,12 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>7,18</t>
+          <t>7,13</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>6,94</t>
+          <t>7,01</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -971,17 +971,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>7,1; 7,37</t>
+          <t>7,09; 7,17</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>6,75; 7,01</t>
+          <t>6,97; 7,04</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>6,97; 7,15</t>
+          <t>7,04; 7,09</t>
         </is>
       </c>
     </row>
